--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/feb-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/feb-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1002,7 +1002,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3134-27-CM26</t>
+          <t>188-92-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,32 +1022,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>No aceptada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARITIMO Y M.M.</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>15079.44</v>
+        <v>8982.120000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>188-92-CM26</t>
+          <t>1704-946-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1083,22 +1083,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8982.120000000001</v>
+        <v>859.89</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1704-946-CM26</t>
+          <t>1020-29-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,37 +1139,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>859.89</v>
+        <v>46156.53</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1020-29-CM26</t>
+          <t>2934-12-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,17 +1205,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.073.200-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ALHUE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>46156.53</v>
+        <v>4435.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2934-12-CM26</t>
+          <t>4401-124-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.073.200-9</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALHUE</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4435.13</v>
+        <v>2875.98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4401-124-CM26</t>
+          <t>3838-26-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,37 +1322,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2875.98</v>
+        <v>33023.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3838-26-CM26</t>
+          <t>3904-79-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,27 +1383,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>33023.45</v>
+        <v>27844.69</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3904-79-CM26</t>
+          <t>3876-16-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,37 +1444,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>27844.69</v>
+        <v>2863.21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3876-16-CM26</t>
+          <t>4099-100-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1515,17 +1515,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.073.300-5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE MARIA PINTO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2863.21</v>
+        <v>4227.59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4099-100-CM26</t>
+          <t>1480074-3-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.073.300-5</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA PINTO</t>
+          <t>MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>NextTime Software S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>99.576.370-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4227.59</v>
+        <v>4460.72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1480074-3-CM26</t>
+          <t>1237404-18-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1632,17 +1632,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>65.293.750-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>CORPORACION CULTURAL MUNICIPAL DE ANCUD</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>NextTime Software S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>99.576.370-2</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4460.72</v>
+        <v>1846.26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1237404-18-CM26</t>
+          <t>3469-112-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,37 +1688,37 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>65.293.750-0</t>
+          <t>69.120.300-k</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL MUNICIPAL DE ANCUD</t>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1846.26</v>
+        <v>28821.15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3469-112-CM26</t>
+          <t>3872-43-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,27 +1759,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>28821.15</v>
+        <v>1523.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2912-80-CM26</t>
+          <t>539119-470-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1815,32 +1815,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.220.702-5</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>Carabineros de Chile - Dirección de Bienestar</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4435.13</v>
+        <v>1056.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>539119-470-CM26</t>
+          <t>1238177-14-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>65.165.009-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1056.9</v>
+        <v>3534.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1238177-14-CM26</t>
+          <t>568658-365-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,27 +1942,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>65.165.009-7</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SE</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3534.3</v>
+        <v>30771.02</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>568658-365-CM26</t>
+          <t>4052-22-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>69.251.200-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>30771.02</v>
+        <v>10000.58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4052-22-CM26</t>
+          <t>2912-80-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.251.200-6</t>
+          <t>69.220.702-5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+          <t>Departamento Administrativo de Salud Municipal.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>10000.58</v>
+        <v>4435.13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3872-43-CM26</t>
+          <t>633-83-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,53 +2115,57 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1523.2</v>
+        <v>565653.41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>633-83-CM26</t>
+          <t>2677-49-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2186,47 +2190,43 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>565653.41</v>
+        <v>37694.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2677-49-CM26</t>
+          <t>2696-18-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>37694.5</v>
+        <v>6416.48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2696-18-CM26</t>
+          <t>3778-54-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2302,22 +2302,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>6416.48</v>
+        <v>12418.36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3778-54-CM26</t>
+          <t>3834-43-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2373,27 +2373,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.486.150-7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>12418.36</v>
+        <v>37961</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3153-41-CM26</t>
+          <t>1238177-28-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2424,37 +2424,37 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.180.500-k</t>
+          <t>65.165.009-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>NextTime Software S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>99.576.370-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>12832.96</v>
+        <v>11138.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3834-43-CM26</t>
+          <t>3016-71-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2485,37 +2485,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.090.500-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE LOLOL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SUPER SOFTWARE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.486.150-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>37961</v>
+        <v>8870.26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1238177-28-CM26</t>
+          <t>3697-180-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2556,27 +2556,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>65.165.009-7</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SE</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>NextTime Software S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>99.576.370-2</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2586,128 +2586,6 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>11138.4</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>3016-71-CM26</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>feb-2026</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>69.090.500-0</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE LOLOL</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>TECNOLOGIA BS SPA</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="n">
-        <v>8870.26</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>3697-180-CM26</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>feb-2026</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>69.180.900-5</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>TECNOLOGIA BS SPA</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="n">
         <v>7096.21</v>
       </c>
     </row>
